--- a/astro-site/public/dl/hotel-checklist-templates/02-hotel-lunch-dinner-buffet-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/02-hotel-lunch-dinner-buffet-checklists.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Place clean serving utensils in every pan</t>
+          <t>Place clean serving utensils in every pan; sneeze guards in place and a sign asking guests to take a clean plate on every trip (FDA 3-306.11, 3-304.16)</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
